--- a/examples/demo_证券虚假陈述集团诉讼/output/证券虚假陈述案件-类案检索清单-20260609.xlsx
+++ b/examples/demo_证券虚假陈述集团诉讼/output/证券虚假陈述案件-类案检索清单-20260609.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="判决要点" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="争点编码" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案例索引" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="裁判分歧清单" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'判决要点'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'争点编码'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'案例索引'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'裁判分歧清单'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2467,4 +2469,251 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>争议问题</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>立场A(件数)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>立场A代表案号</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>立场B(件数)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>立场B代表案号</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>其他立场</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>样本提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>重大性</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>具有重大性（1）</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>（2022）示74民初0301号</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>不具重大性（1）</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>（2023）示01民初0212号</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>揭露日认定</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>立案调查公告日（1）</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>（2022）示74民初0301号</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>更正公告日（1）</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>（2022）示74民初0388号</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr"/>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>交易因果关系</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>推定成立（2）</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>（2022）示74民初0301号；（2022）示74民初0290号</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>不成立（1）</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>（2023）示01民初0212号</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>损失因果关系</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>扣除系统风险15%（1）</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>（2022）示74民初0301号</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>非系统风险亦扣除（1）</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>（2023）示民终0061号</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>责任形态</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>缩减赔偿范围（1）</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>（2023）示民终0061号</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>连带责任（1）</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>（2023）示01民初0276号</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>